--- a/output/pdf_financials_xlsx/RNCH.xlsx
+++ b/output/pdf_financials_xlsx/RNCH.xlsx
@@ -6223,16 +6223,16 @@
         <v>0</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>0.6517500000000001</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>0.6517500000000001</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>0.6517500000000001</v>
       </c>
       <c r="R92" s="3" t="n">
-        <v>0</v>
+        <v>0.690983</v>
       </c>
     </row>
     <row r="93">
@@ -9779,7 +9779,11 @@
           <t>Reserves (Note 7)</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
           <t>-</t>
@@ -14795,7 +14799,11 @@
           <t>Reserves (Note 8) 651,750</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr"/>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E60" t="inlineStr">
         <is>
           <t>-</t>
@@ -16526,7 +16534,11 @@
           <t>Reserves (Note 7) 102,800</t>
         </is>
       </c>
-      <c r="D77" t="inlineStr"/>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E77" t="inlineStr">
         <is>
           <t>-</t>
@@ -55822,7 +55834,7 @@
         </is>
       </c>
       <c r="H470" s="5" t="n">
-        <v>0.008</v>
+        <v>-0.008</v>
       </c>
       <c r="I470" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/RNCH.xlsx
+++ b/output/pdf_financials_xlsx/RNCH.xlsx
@@ -1067,34 +1067,34 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.994</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.95</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.21</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.29</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.279</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.272</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>0.054</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>0.034</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>0.014</v>
       </c>
       <c r="L12" s="1" t="inlineStr">
         <is>
@@ -2129,34 +2129,34 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-276.702</v>
+        <v>-277.696</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-32.032</v>
+        <v>-32.052</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-6.748</v>
+        <v>-7.698</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-6.202</v>
+        <v>-6.412</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-1.153998</v>
+        <v>-1.443998</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-3.201</v>
+        <v>-3.48</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-2.935</v>
+        <v>-3.207</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-19.634</v>
+        <v>-19.688</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-4.126</v>
+        <v>-4.16</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-6.714</v>
+        <v>-6.728</v>
       </c>
       <c r="L27" s="1" t="inlineStr">
         <is>
@@ -2255,34 +2255,34 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-276.291</v>
+        <v>-277.285</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-32.028</v>
+        <v>-32.048</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-6.748</v>
+        <v>-7.698</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-6.202</v>
+        <v>-6.412</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-1.153998</v>
+        <v>-1.443998</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-3.201</v>
+        <v>-3.48</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-2.935</v>
+        <v>-3.207</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-19.634</v>
+        <v>-19.688</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-4.126</v>
+        <v>-4.16</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-6.714</v>
+        <v>-6.728</v>
       </c>
       <c r="L29" s="1" t="inlineStr">
         <is>
@@ -2612,19 +2612,19 @@
         <v>0</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.071968</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.051315</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>1.008994</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>0.457507</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>0.142872</v>
       </c>
     </row>
     <row r="35">
@@ -2732,19 +2732,19 @@
         <v>0</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>0.071968</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>0.051315</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>1.008994</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>0.457507</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0</v>
+        <v>0.142872</v>
       </c>
     </row>
     <row r="37">
@@ -3452,7 +3452,7 @@
         <v>0</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.074388</v>
+        <v>0.00242</v>
       </c>
       <c r="O48" s="3" t="n">
         <v>0</v>
@@ -8093,10 +8093,10 @@
         <v>0</v>
       </c>
       <c r="J124" s="3" t="n">
-        <v>0</v>
+        <v>-0.019</v>
       </c>
       <c r="K124" s="3" t="n">
-        <v>0</v>
+        <v>-0.008999999999999999</v>
       </c>
       <c r="L124" s="1" t="inlineStr">
         <is>
@@ -8153,10 +8153,10 @@
         <v>0</v>
       </c>
       <c r="J125" s="3" t="n">
-        <v>0</v>
+        <v>-0.019</v>
       </c>
       <c r="K125" s="3" t="n">
-        <v>0</v>
+        <v>-0.008999999999999999</v>
       </c>
       <c r="L125" s="1" t="inlineStr">
         <is>
@@ -8969,7 +8969,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -12462,7 +12462,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -13777,7 +13777,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -15401,7 +15401,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -33855,7 +33855,11 @@
           <t>Finance lease repayments</t>
         </is>
       </c>
-      <c r="D250" t="inlineStr"/>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E250" t="inlineStr">
         <is>
           <t>-</t>
@@ -35009,7 +35013,11 @@
           <t>Finance lease repayment</t>
         </is>
       </c>
-      <c r="D262" t="inlineStr"/>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E262" t="inlineStr">
         <is>
           <t>-</t>
@@ -49352,7 +49360,7 @@
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E405" t="inlineStr">
@@ -50142,7 +50150,7 @@
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E413" t="inlineStr">
@@ -55007,7 +55015,7 @@
       </c>
       <c r="D462" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E462" t="inlineStr">
@@ -58855,7 +58863,7 @@
       </c>
       <c r="D500" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E500" s="5" t="n">

--- a/output/pdf_financials_xlsx/RNCH.xlsx
+++ b/output/pdf_financials_xlsx/RNCH.xlsx
@@ -7829,7 +7829,7 @@
         </is>
       </c>
       <c r="B120" s="3" t="n">
-        <v>0</v>
+        <v>-0.198</v>
       </c>
       <c r="C120" s="3" t="n">
         <v>0</v>
@@ -7864,10 +7864,10 @@
         </is>
       </c>
       <c r="M120" s="3" t="n">
-        <v>0</v>
+        <v>0.8126370000000001</v>
       </c>
       <c r="N120" s="3" t="n">
-        <v>0</v>
+        <v>5.0668</v>
       </c>
       <c r="O120" s="3" t="n">
         <v>0</v>
@@ -31649,7 +31649,11 @@
           <t>Issuance of common shares, net of issuance costs</t>
         </is>
       </c>
-      <c r="D228" t="inlineStr"/>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>IssuanceOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E228" t="inlineStr">
         <is>
           <t>-</t>
@@ -43853,7 +43857,11 @@
           <t>Issuance of common shares, net of issue costs</t>
         </is>
       </c>
-      <c r="D350" t="inlineStr"/>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>IssuanceOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E350" s="5" t="n">
         <v>-0.198</v>
       </c>
